--- a/input/sample-tests.xlsx
+++ b/input/sample-tests.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="525" windowWidth="14055" windowHeight="4050"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualTestCases" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="ManualTestCases" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="76">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -45,10 +45,10 @@
     </r>
     <r>
       <rPr>
+        <color theme="1"/>
+        <family val="2"/>
         <sz val="10"/>
-        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
       </rPr>
       <t>standard_user</t>
     </r>
@@ -62,10 +62,10 @@
     </r>
     <r>
       <rPr>
+        <color theme="1"/>
+        <family val="2"/>
         <sz val="10"/>
-        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
       </rPr>
       <t>secret_sauce</t>
     </r>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>Login error message is displayed</t>
+  </si>
+  <si>
+    <t>Login was attempted with invalid credentials</t>
+  </si>
+  <si>
+    <t>Verify login error message</t>
   </si>
   <si>
     <t>TC-SD-003</t>
@@ -263,14 +269,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -279,17 +285,11 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -659,9 +659,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
@@ -670,7 +670,7 @@
     <col min="5" max="5" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="30">
+    <row r="1" ht="30" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -687,7 +687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75.75">
+    <row r="2" ht="75.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -704,7 +704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="75.75">
+    <row r="3" ht="75.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -721,7 +721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="75">
+    <row r="4" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -738,7 +738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="75">
+    <row r="5" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -755,7 +755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="75.75">
+    <row r="6" ht="75.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="75">
+    <row r="7" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -789,7 +789,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="90">
+    <row r="8" ht="90" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -806,29 +806,29 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="75">
+    <row r="9" ht="90" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="75">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>27</v>
@@ -840,219 +840,219 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="75">
+    <row r="11" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="3" t="s">
+    </row>
+    <row r="12" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="60">
-      <c r="A12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="3" t="s">
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="75">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="14" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="60">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="B14" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="60">
-      <c r="A15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="C15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="75">
+    <row r="16" ht="60" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="3" t="s">
+    </row>
+    <row r="17" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="75">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="3" t="s">
+    </row>
+    <row r="18" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="90">
-      <c r="A18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="3" t="s">
+    </row>
+    <row r="19" ht="90" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="90">
-      <c r="A19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="3" t="s">
+    </row>
+    <row r="20" ht="90" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="75">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="60">
+    </row>
+    <row r="21" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="105">
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" ht="105" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="105">
-      <c r="A23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>60</v>
@@ -1061,15 +1061,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="105">
+    <row r="24" ht="105" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>62</v>
@@ -1078,15 +1078,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="105">
+    <row r="25" ht="105" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>64</v>
@@ -1095,46 +1095,46 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="90">
+    <row r="26" ht="105" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="3" t="s">
+    </row>
+    <row r="27" ht="90" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="90">
-      <c r="A27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="105">
+    </row>
+    <row r="28" ht="90" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>71</v>
@@ -1146,8 +1146,25 @@
         <v>73</v>
       </c>
     </row>
+    <row r="29" ht="105" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>